--- a/docs/需求流程-骰娘系统与AI全景规划.xlsx
+++ b/docs/需求流程-骰娘系统与AI全景规划.xlsx
@@ -56,13 +56,13 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="001565C0"/>
+      <color rgb="00E65100"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00E65100"/>
+      <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -139,10 +139,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,7 +154,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1103,17 +1103,17 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>handleInbound：归一→brain.handle→transformReplies 增强→channel.send→事件广播</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>良好</t>
+          <t>handleInbound：归一→brain.handle→transformReplies 增强→channel.send→事件广播；boton/botoff 仅登记未在响应链路拦截</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>有债（群开关未拦截）</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>U8-7 打通前置拦截</t>
         </is>
       </c>
     </row>
@@ -1140,17 +1140,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>状态机 stopped→starting→awaiting-scan/slider/sms→running；签名服务风控治理（可关）；登录守卫频控；断线自动重连+假在线巡检；按账号隔离 sessionDir</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>良好</t>
+          <t>状态机 stopped→starting→awaiting-scan/slider/sms→running；签名服务风控治理（可关）；登录守卫频控；断线自动重连+假在线巡检；按账号隔离 sessionDir；协议可选（android/aPad/watch/iPad…）</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>有债（默认协议互踢）</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>P0-5/P0-6 重连闭环已落实</t>
+          <t>U8-5 将默认改 aPad 与手机共存</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
           <t>纯渲染函数 + app.js 事件绑定；UMD 双通道挂载（Node require 与浏览器全局并存）</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>已修复待发版</t>
         </is>
@@ -1547,17 +1547,17 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>统一开关体系（enabled+features）；acceptableOptimize 数值一致性校验，引擎原文永不被改写；KP 建议仅面板展示</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>良好</t>
+          <t>统一开关体系（enabled+features）；acceptableOptimize 数值一致性校验，引擎原文永不被改写；KP 建议仅面板展示；开关仅全局粒度无按群覆盖</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>有债（群级粒度缺失）</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>U8-7 补 groupOverrides</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
           <t>esbuild 单 bundle（714KB，-13%）；多 script 按序聚合；源码尚未按视图拆分</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>有债（U12 拆分）</t>
         </is>
@@ -1661,7 +1661,7 @@
           <t>367 项：静态断言为主 + 骰娘 30 条指令回归 + 打包后浏览器全局挂载沙箱检查（新）</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>有债（行为级不足）</t>
         </is>
@@ -1758,7 +1758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1772,7 +1772,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>骰娘系统与 AI · 演进路线（U8~U12 五批 22 个迭代点；编号接续既有 U 系列）</t>
+          <t>骰娘系统与 AI · 演进路线（U8~U12 五批 26 个迭代点；编号接续既有 U 系列，U8-5~U8-8 为连接与风控专项）</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="E1" s="2">
-        <f>COUNTA(A4:A25)</f>
+        <f>COUNTA(A4:A29)</f>
         <v/>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="G1" s="2">
-        <f>COUNTIF(F4:F25,"P0")+COUNTIF(F4:F25,"P1")</f>
+        <f>COUNTIF(F4:F29,"P0")+COUNTIF(F4:F29,"P1")</f>
         <v/>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1926,7 +1926,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -1967,22 +1967,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>U9 AI 深化与成本</t>
+          <t>U8 骰娘连接与运维</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>U9-1 场景记忆自动回写闭环</t>
+          <t>U8-5 默认平板协议不挤本体</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>plotSummary/story 等场景运行后自动 append 要点，带条数上限与去重裁剪</t>
+          <t>qqdirect 默认协议 android→aPad（官方允许手机+平板同时在线互不挤踢）；登录卡片标注当前协议与互踢提示，android 保留为显式可选并在选择时警告；登录诊断 diagnostics 增加协议与手机端共存关系说明</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>连续运行同一场景，记忆尾部单调更新且超限裁剪；回写失败不影响主流程</t>
+          <t>默认配置登录后手机端官方 QQ 保持在线；显式选 android 时提示将与手机端互踢；协议归一与回归更新</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1990,36 +1990,36 @@
           <t>无</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>U9 AI 深化与成本</t>
+          <t>U8 骰娘连接与运维</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>U9-2 JSON 强约束全场景覆盖</t>
+          <t>U8-6 内置会话面板（骰娘 QQ 界面）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>response_format=json_object 从 rawJsonReply 推广到全部结构化场景（persona/entities/registration/scenario/audit 等）</t>
+          <t>dice-ui 新增分区「会话」：左侧群/好友列表 + 右侧消息流；实时消息消费 dice-qq:event 广播（normalize 扩展群名/发送者归一）；打开会话拉取最近历史（icqq getChatHistory 桥接）；底部发送框支持手动聊天与骰令（IPC diceQq:sendGroup/sendPrivate）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>各场景解析成功率上升、解析重试次数下降（诊断计数对比）</t>
+          <t>登录后可在应用内读群聊、手动发言、发骰令，不依赖手机 QQ；断线时面板置灰提示；未登录不崩溃；回归含 sim 通道等价检查</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>U8-5</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -2031,54 +2031,54 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>U9 AI 深化与成本</t>
+          <t>U8 骰娘连接与运维</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>U9-3 按场景用量看板</t>
+          <t>U8-7 群级骰娘/AI 开关</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>ai:usage 扩展 per-scene token/耗时计数，设置页展示各场景消耗 Top</t>
+          <t>会话面板每群两个开关：「骰娘响应」迁移 session.remote.groups 并打通 brain.handle 前置拦截（关闭后不解析不回复）；「AI 增强」新增 settings.dice.aiSwitches.groupOverrides[群号]，dice-ai 判定先查群覆盖再落全局；开关随会话状态持久化</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>看板可见近 N 次各场景消耗；重置入口有效</t>
+          <t>关群后 .r 不回复、插话/表情包/润色零请求；面板开关即时生效；黑白名单优先级不变；回归覆盖拦截链路</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>U9-2</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>U8-6</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>U9 AI 深化与成本</t>
+          <t>U8 骰娘连接与运维</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>U9-4 结构化输出校验修复</t>
+          <t>U8-8 风控治理强化（发送侧节流与可观测）</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>分幕/取卡结果 schema 校验失败自动纠偏一轮（复用现有质量闸与纠偏通道）</t>
+          <t>出站统一消息队列：默认限速（如 4 条/分钟可配，0=不限）+ 连续风控/失败指数退避；长回复分片间隔随机化；新群首次响应冷却 60s；连接中心新增风控事件计数与最近事件展示；文档写明最佳实践（专用小号/签名服务/协议选择/避免刷屏）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>坏 JSON 自动修复率可观测；不再因格式漂移产生空段</t>
+          <t>限速器单测（令牌桶语义）；风控事件连接中心可见；被风控后自动退避并可恢复；明确告知无法保证 100% 不被风控</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -2100,49 +2100,49 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>U9-5 关系网增量推理</t>
+          <t>U9-1 场景记忆自动回写闭环</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>指纹缓存（P1-3 已做）基础上仅对变更实体增量推理，未变更部分直接复用</t>
+          <t>plotSummary/story 等场景运行后自动 append 要点，带条数上限与去重裁剪</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>卡片微改后推理 token 显著下降；npm run bench 对比可证</t>
+          <t>连续运行同一场景，记忆尾部单调更新且超限裁剪；回写失败不影响主流程</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>P1-3（已落实）</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>U10 可访问性与交互</t>
+          <t>U9 AI 深化与成本</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>U10-1 表单 label 程序化关联</t>
+          <t>U9-2 JSON 强约束全场景覆盖</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>统一「表单行」生成函数输出 for/id 配对，存量 121 处批量补齐（UI 审计 P1-1）</t>
+          <t>response_format=json_object 从 rawJsonReply 推广到全部结构化场景（persona/entities/registration/scenario/audit 等）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>全库 label 关联率 100%；审计复测 P1-1 消除</t>
+          <t>各场景解析成功率上升、解析重试次数下降（诊断计数对比）</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -2159,54 +2159,54 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>U10 可访问性与交互</t>
+          <t>U9 AI 深化与成本</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>U10-2 toast/提示条读屏可感知</t>
+          <t>U9-3 按场景用量看板</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>#toasts 加 aria-live=polite；.ai-busy 加 role=status；错误类 toast 用 role=alert（P1-2）</t>
+          <t>ai:usage 扩展 per-scene token/耗时计数，设置页展示各场景消耗 Top</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>保存/错误/AI 开始结束均有读屏播报；aria 全库计数 &gt;0</t>
+          <t>看板可见近 N 次各场景消耗；重置入口有效</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>U9-2</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>U10 可访问性与交互</t>
+          <t>U9 AI 深化与成本</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>U10-3 弹窗焦点圈闭与恢复</t>
+          <t>U9-4 结构化输出校验修复</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>模态 focus trap + 背景容器 inert + 关闭后焦点回触发元素（P1-3）</t>
+          <t>分幕/取卡结果 schema 校验失败自动纠偏一轮（复用现有质量闸与纠偏通道）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Tab 不逃逸遮罩；关闭后焦点回原按钮；Esc 闭环保持</t>
+          <t>坏 JSON 自动修复率可观测；不再因格式漂移产生空段</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -2223,27 +2223,27 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>U10 可访问性与交互</t>
+          <t>U9 AI 深化与成本</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>U10-4 非按钮可点击整改</t>
+          <t>U9-5 关系网增量推理</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>14 处 div/span/td 挂 onclick 改为 button 或补 role+tabindex+键盘回车（P2-1）</t>
+          <t>指纹缓存（P1-3 已做）基础上仅对变更实体增量推理，未变更部分直接复用</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>键盘可达；审计复测清零</t>
+          <t>卡片微改后推理 token 显著下降；npm run bench 对比可证</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>P1-3（已落实）</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>U10-5 命中区与焦点环</t>
+          <t>U10-1 表单 label 程序化关联</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>小按钮最小命中区 32×32；命令面板 :focus-within 高亮；2 处 z-index 魔数归队 2~500 体系（P2-3/P2-4/P3）</t>
+          <t>统一「表单行」生成函数输出 for/id 配对，存量 121 处批量补齐（UI 审计 P1-1）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>触控板误触下降；审计复测提分（目标 ≥16/20）</t>
+          <t>全库 label 关联率 100%；审计复测 P1-1 消除</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -2278,31 +2278,31 @@
           <t>无</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>U11 性能与体积</t>
+          <t>U10 可访问性与交互</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>U11-1 全局搜索渲染收敛</t>
+          <t>U10-2 toast/提示条读屏可感知</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>搜索结果渲染 diff / 仅重排 Top N（P1-12 防抖之后的二次项，针对 _gPaint 全量重绘）</t>
+          <t>#toasts 加 aria-live=polite；.ai-busy 加 role=status；错误类 toast 用 role=alert（P1-2）</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>3000 卡规模输入到出结果耗时对比下降；npm run bench 留档</t>
+          <t>保存/错误/AI 开始结束均有读屏播报；aria 全库计数 &gt;0</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -2310,7 +2310,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2319,54 +2319,54 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>U11 性能与体积</t>
+          <t>U10 可访问性与交互</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>U11-2 卡片视口虚拟化</t>
+          <t>U10-3 弹窗焦点圈闭与恢复</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>上千卡仅渲染可见区，滚动动态挂载（P2-13）</t>
+          <t>模态 focus trap + 背景容器 inert + 关闭后焦点回触发元素（P1-3）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>8000 卡滚动帧率达标；交叉引用/搜索功能行为等价</t>
+          <t>Tab 不逃逸遮罩；关闭后焦点回原按钮；Esc 闭环保持</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>U11-1</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>U11 性能与体积</t>
+          <t>U10 可访问性与交互</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>U11-3 打包体积瘦身</t>
+          <t>U10-4 非按钮可点击整改</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>依赖树审计：pdfjs 字体/cmaps、xlsx slim 深度裁剪（P2-16 残余项）</t>
+          <t>14 处 div/span/td 挂 onclick 改为 button 或补 role+tabindex+键盘回车（P2-1）</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>绿色版体积较 3.3.2（113MB）明显下降；功能回归全绿</t>
+          <t>键盘可达；审计复测清零</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -2383,22 +2383,22 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>U11 性能与体积</t>
+          <t>U10 可访问性与交互</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>U11-4 启动链路收尾</t>
+          <t>U10-5 命中区与焦点环</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>骰娘 hub/通道确认懒装配；bootData 后首帧指标化埋点</t>
+          <t>小按钮最小命中区 32×32；命令面板 :focus-within 高亮；2 处 z-index 魔数归队 2~500 体系（P2-3/P2-4/P3）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>冷启动到可交互时间可观测且下降；icqq 保持懒加载不回退</t>
+          <t>触控板误触下降；审计复测提分（目标 ≥16/20）</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -2415,22 +2415,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>U12 工程化与测试债</t>
+          <t>U11 性能与体积</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>U12-1 渲染层源码拆分</t>
+          <t>U11-1 全局搜索渲染收敛</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>app.js（747KB）按视图模块拆分 + esbuild 聚合（P2-17 完整形态）；构建期 fail-fast 校验浏览器全局挂载（把打包沙箱检查前移到 build:renderer）</t>
+          <t>搜索结果渲染 diff / 仅重排 Top N（P1-12 防抖之后的二次项，针对 _gPaint 全量重绘）</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>拆分后 npm test/verify 全绿；bundle 行为等价；构建期可拦截 UMD 类回归</t>
+          <t>3000 卡规模输入到出结果耗时对比下降；npm run bench 留档</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -2438,7 +2438,7 @@
           <t>无</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -2447,94 +2447,222 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>U12 工程化与测试债</t>
+          <t>U11 性能与体积</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>U12-2 行为级测试补强</t>
+          <t>U11-2 卡片视口虚拟化</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>dice-net 通道状态机（重连/假在线/kickoff）与长文本链路 mock 行为测试</t>
+          <t>上千卡仅渲染可见区，滚动动态挂载（P2-13）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>核心链路行为用例覆盖；静态断言占比下降；CI 全绿时间不显著变长</t>
+          <t>8000 卡滚动帧率达标；交叉引用/搜索功能行为等价</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>U11-1</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>U12 工程化与测试债</t>
+          <t>U11 性能与体积</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>U12-3 发布流水线一键化</t>
+          <t>U11-3 打包体积瘦身</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>tools/release.js 串：版本三处同步→npm test→build→tag→push→publish→Release 资产自检</t>
+          <t>依赖树审计：pdfjs 字体/cmaps、xlsx slim 深度裁剪（P2-16 残余项）</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>一条命令完成发版并自检线上资产与 latest 指向；漏项即中止</t>
+          <t>绿色版体积较 3.3.2（113MB）明显下降；功能回归全绿</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>U12-1</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>U11 性能与体积</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>U11-4 启动链路收尾</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>骰娘 hub/通道确认懒装配；bootData 后首帧指标化埋点</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>冷启动到可交互时间可观测且下降；icqq 保持懒加载不回退</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>U12 工程化与测试债</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>U12-1 渲染层源码拆分</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>app.js（747KB）按视图模块拆分 + esbuild 聚合（P2-17 完整形态）；构建期 fail-fast 校验浏览器全局挂载（把打包沙箱检查前移到 build:renderer）</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>拆分后 npm test/verify 全绿；bundle 行为等价；构建期可拦截 UMD 类回归</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>U12 工程化与测试债</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>U12-2 行为级测试补强</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>dice-net 通道状态机（重连/假在线/kickoff）与长文本链路 mock 行为测试</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>核心链路行为用例覆盖；静态断言占比下降；CI 全绿时间不显著变长</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>U12 工程化与测试债</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>U12-3 发布流水线一键化</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>tools/release.js 串：版本三处同步→npm test→build→tag→push→publish→Release 资产自检</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>一条命令完成发版并自检线上资产与 latest 指向；漏项即中止</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>U12-1</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>U12 工程化与测试债</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>U12-4 文档发版联动</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>CHANGELOG/DEVLOG/Wiki 同步检查并入 release.js</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>版本号/文档漏改时流水线报错并给出待改清单</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>U12-3</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2552,7 +2680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2567,7 +2695,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>债务与对策映射（15 条）｜状态统计：</t>
+          <t>债务与对策映射（18 条）｜状态统计：</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
@@ -2576,7 +2704,7 @@
         </is>
       </c>
       <c r="D1" s="2">
-        <f>COUNTIF(G4:G18,"*已修*")</f>
+        <f>COUNTIF(G4:G21,"*已修*")</f>
         <v/>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -2585,7 +2713,7 @@
         </is>
       </c>
       <c r="F1" s="2">
-        <f>COUNTIF(G4:G18,"待启动")</f>
+        <f>COUNTIF(G4:G21,"待启动")</f>
         <v/>
       </c>
     </row>
@@ -3176,6 +3304,117 @@
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>本轮需求盘点</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>默认 android 协议登录会挤掉手机端本体 QQ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>DEFAULT_PLATFORM='android' 的历史选择，未默认提供可与手机共存的协议</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>默认 aPad 平板协议（官方支持手机+平板共存）+ 协议选择警告</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>U8-5</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>本轮需求盘点</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>boton/botoff 仅登记到会话状态未真正拦截响应；AI 开关仅全局粒度无按群覆盖</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>开关登记与消息分发链路解耦不完整；aiSwitches 缺群维度</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>brain.handle 前置拦截 + groupOverrides 群覆盖</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>U8-7</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>待启动</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>本轮需求盘点</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>发送侧无节流，活跃群原速直发易触发腾讯风控</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>出站直连 channel.send 无队列与退避</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>统一限速队列 + 指数退避 + 风控事件计数</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>U8-8</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>待启动</t>
         </is>
